--- a/data.mn/public/datasets/meat-production-by-region-en.xlsx
+++ b/data.mn/public/datasets/meat-production-by-region-en.xlsx
@@ -413,13 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -444,11 +439,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5960.3</v>
+        <v>74919.5</v>
       </c>
     </row>
     <row r="3">
@@ -470,11 +465,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47118.5</v>
+        <v>82585.7</v>
       </c>
     </row>
     <row r="5">
@@ -483,11 +478,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74919.5</v>
+        <v>5960.3</v>
       </c>
     </row>
     <row r="6">
@@ -496,11 +491,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82585.7</v>
+        <v>47118.5</v>
       </c>
     </row>
     <row r="7">
@@ -509,11 +504,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5652.8</v>
+        <v>66195.5</v>
       </c>
     </row>
     <row r="8">
@@ -522,11 +517,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Eastern region</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40640</v>
+        <v>48816.7</v>
       </c>
     </row>
     <row r="9">
@@ -535,11 +530,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eastern region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48816.7</v>
+        <v>90042.89999999999</v>
       </c>
     </row>
     <row r="10">
@@ -548,11 +543,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66195.5</v>
+        <v>5652.8</v>
       </c>
     </row>
     <row r="11">
@@ -561,11 +556,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90042.89999999999</v>
+        <v>40640</v>
       </c>
     </row>
     <row r="12">
@@ -574,11 +569,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5198.9</v>
+        <v>68650</v>
       </c>
     </row>
     <row r="13">
@@ -587,11 +582,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Eastern region</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45375.9</v>
+        <v>48601.6</v>
       </c>
     </row>
     <row r="14">
@@ -600,11 +595,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eastern region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48601.6</v>
+        <v>95589.10000000001</v>
       </c>
     </row>
     <row r="15">
@@ -613,11 +608,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68650</v>
+        <v>5198.9</v>
       </c>
     </row>
     <row r="16">
@@ -626,11 +621,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>95589.10000000001</v>
+        <v>45375.9</v>
       </c>
     </row>
     <row r="17">
@@ -639,11 +634,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5692.3</v>
+        <v>76901.89999999999</v>
       </c>
     </row>
     <row r="18">
@@ -665,11 +660,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56826.4</v>
+        <v>111459.4</v>
       </c>
     </row>
     <row r="20">
@@ -678,11 +673,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>76901.89999999999</v>
+        <v>5692.3</v>
       </c>
     </row>
     <row r="21">
@@ -691,11 +686,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>111459.4</v>
+        <v>56826.4</v>
       </c>
     </row>
     <row r="22">
@@ -704,11 +699,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4854.5</v>
+        <v>74263.60000000001</v>
       </c>
     </row>
     <row r="23">
@@ -730,11 +725,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57336.7</v>
+        <v>107655.9</v>
       </c>
     </row>
     <row r="25">
@@ -743,11 +738,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74263.60000000001</v>
+        <v>4854.5</v>
       </c>
     </row>
     <row r="26">
@@ -756,11 +751,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>107655.9</v>
+        <v>57336.7</v>
       </c>
     </row>
     <row r="27">
@@ -769,11 +764,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8709.6</v>
+        <v>118371.9</v>
       </c>
     </row>
     <row r="28">
@@ -795,11 +790,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>88039.8</v>
+        <v>168339.1</v>
       </c>
     </row>
     <row r="30">
@@ -808,11 +803,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>118371.9</v>
+        <v>8709.6</v>
       </c>
     </row>
     <row r="31">
@@ -821,11 +816,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>168339.1</v>
+        <v>88039.8</v>
       </c>
     </row>
     <row r="32">
@@ -834,11 +829,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7647.1</v>
+        <v>108614.3</v>
       </c>
     </row>
     <row r="33">
@@ -860,11 +855,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>75848.7</v>
+        <v>137929.3</v>
       </c>
     </row>
     <row r="35">
@@ -873,11 +868,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>108614.3</v>
+        <v>7647.1</v>
       </c>
     </row>
     <row r="36">
@@ -886,11 +881,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>137929.3</v>
+        <v>75848.7</v>
       </c>
     </row>
     <row r="37">
@@ -899,11 +894,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8626.4</v>
+        <v>107362.9</v>
       </c>
     </row>
     <row r="38">
@@ -925,11 +920,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>91259.89999999999</v>
+        <v>175058.9</v>
       </c>
     </row>
     <row r="40">
@@ -938,11 +933,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>107362.9</v>
+        <v>8626.4</v>
       </c>
     </row>
     <row r="41">
@@ -951,11 +946,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>175058.9</v>
+        <v>91259.89999999999</v>
       </c>
     </row>
     <row r="42">
@@ -964,11 +959,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9532.700000000001</v>
+        <v>121236.9</v>
       </c>
     </row>
     <row r="43">
@@ -990,11 +985,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>117543.1</v>
+        <v>184093.6</v>
       </c>
     </row>
     <row r="45">
@@ -1003,11 +998,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>121236.9</v>
+        <v>9532.700000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1016,11 +1011,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>184093.6</v>
+        <v>117543.1</v>
       </c>
     </row>
     <row r="47">
@@ -1029,11 +1024,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8094.4</v>
+        <v>120970.8</v>
       </c>
     </row>
     <row r="48">
@@ -1046,7 +1041,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>95406.10000000001</v>
+        <v>95405.7</v>
       </c>
     </row>
     <row r="49">
@@ -1055,11 +1050,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>113413.6</v>
+        <v>205933.2</v>
       </c>
     </row>
     <row r="50">
@@ -1068,11 +1063,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>125109.2</v>
+        <v>8094.4</v>
       </c>
     </row>
     <row r="51">
@@ -1081,11 +1076,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>203005.9</v>
+        <v>113413</v>
       </c>
     </row>
     <row r="52">
@@ -1094,11 +1089,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7410.6</v>
+        <v>152123.5</v>
       </c>
     </row>
     <row r="53">
@@ -1111,7 +1106,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>106995.4</v>
+        <v>106995</v>
       </c>
     </row>
     <row r="54">
@@ -1120,11 +1115,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>156941.4</v>
+        <v>320043.4</v>
       </c>
     </row>
     <row r="55">
@@ -1133,11 +1128,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>159589.1</v>
+        <v>7410.6</v>
       </c>
     </row>
     <row r="56">
@@ -1146,11 +1141,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>313579.5</v>
+        <v>159588.5</v>
       </c>
     </row>
     <row r="57">
@@ -1159,11 +1154,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9341.299999999999</v>
+        <v>135806</v>
       </c>
     </row>
     <row r="58">
@@ -1176,7 +1171,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>84610.10000000001</v>
+        <v>84609.7</v>
       </c>
     </row>
     <row r="59">
@@ -1185,11 +1180,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>102702.7</v>
+        <v>174511.1</v>
       </c>
     </row>
     <row r="60">
@@ -1198,11 +1193,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>141665.8</v>
+        <v>9341.299999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1211,11 +1206,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>174359.3</v>
+        <v>102702.1</v>
       </c>
     </row>
     <row r="62">
@@ -1224,11 +1219,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9161.299999999999</v>
+        <v>158188.1</v>
       </c>
     </row>
     <row r="63">
@@ -1241,7 +1236,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>106085.5</v>
+        <v>106085.2</v>
       </c>
     </row>
     <row r="64">
@@ -1250,11 +1245,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>164404.8</v>
+        <v>207700.1</v>
       </c>
     </row>
     <row r="65">
@@ -1263,11 +1258,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>169011.8</v>
+        <v>9161.200000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1276,11 +1271,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>205303.2</v>
+        <v>169011.3</v>
       </c>
     </row>
     <row r="67">
@@ -1289,11 +1284,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6492.6</v>
+        <v>187717.5</v>
       </c>
     </row>
     <row r="68">
@@ -1302,11 +1297,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Eastern region</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>109642.8</v>
+        <v>128377.4</v>
       </c>
     </row>
     <row r="69">
@@ -1315,11 +1310,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eastern region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>115241.4</v>
+        <v>230885.7</v>
       </c>
     </row>
     <row r="70">
@@ -1328,11 +1323,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>173757.3</v>
+        <v>6719.1</v>
       </c>
     </row>
     <row r="71">
@@ -1341,11 +1336,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>216948.7</v>
+        <v>114859.6</v>
       </c>
     </row>
     <row r="72">
@@ -1354,11 +1349,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ulaanbaatar</t>
+          <t>Central region</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5149.7</v>
+        <v>116421.5</v>
       </c>
     </row>
     <row r="73">
@@ -1371,7 +1366,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>58589</v>
+        <v>66796.7</v>
       </c>
     </row>
     <row r="74">
@@ -1380,11 +1375,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Western region</t>
+          <t>Khangai region</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>88604.10000000001</v>
+        <v>176245.5</v>
       </c>
     </row>
     <row r="75">
@@ -1393,11 +1388,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Central region</t>
+          <t>Ulaanbaatar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>121646.6</v>
+        <v>6410.1</v>
       </c>
     </row>
     <row r="76">
@@ -1406,11 +1401,76 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Khangai region</t>
+          <t>Western region</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>176453.7</v>
+        <v>87262.89999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Central region</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>167509.088</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Eastern region</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>94900.167</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Khangai region</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>265663.375</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ulaanbaatar</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2588.572</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Western region</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>169211.179</v>
       </c>
     </row>
   </sheetData>
